--- a/sendcleared-outreach-tracker.xlsx
+++ b/sendcleared-outreach-tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timothyarmstead/Sendcleared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D539DDF7-9E9B-0E41-9A48-7E23B255FCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F41755-2DE4-5245-9C60-23B55D1F12AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6920" yWindow="1620" windowWidth="29900" windowHeight="17100" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6640" yWindow="2320" windowWidth="29900" windowHeight="17100" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Playbook" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="358">
   <si>
     <t>SendCleared — Daily Outreach Playbook  |  1 Hour / Day</t>
   </si>
@@ -1115,6 +1115,24 @@
   </si>
   <si>
     <t>https://www.linkedin.com/in/aranchagomezarranz/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/yurii-zuban/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lana-williams-9b4442b8/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/shaun-reynolds-email-marketing/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kate-reeves-0b068a3a/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sylvester-swea-b2a1b87b/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/louise-rebecca-thomas/</t>
   </si>
 </sst>
 </file>
@@ -1253,19 +1271,6 @@
   </cellStyleXfs>
   <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1292,6 +1297,19 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1571,947 +1589,947 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="3">
         <v>46230</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="11"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="3">
         <v>46231</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I7" s="11"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+      <c r="A8" s="2">
         <v>3</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="3">
         <v>46232</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="11"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="2">
         <v>4</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="3">
         <v>46233</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I9" s="11"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+      <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="3">
         <v>46234</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="11"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
+      <c r="A12" s="2">
         <v>6</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="3">
         <v>46237</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="11" t="s">
+      <c r="G12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="11"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+      <c r="A13" s="2">
         <v>7</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="3">
         <v>46238</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="11" t="s">
+      <c r="E13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="11" t="s">
+      <c r="G13" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="11"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+      <c r="A14" s="2">
         <v>8</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="3">
         <v>46239</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="11"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+      <c r="A15" s="2">
         <v>9</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="3">
         <v>46240</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I15" s="11"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9">
+      <c r="A16" s="2">
         <v>10</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="3">
         <v>46241</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="11"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="A18" s="2">
         <v>11</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="3">
         <v>46244</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="11"/>
+      <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9">
+      <c r="A19" s="2">
         <v>12</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="3">
         <v>46245</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="11" t="s">
+      <c r="F19" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G19" s="11" t="s">
+      <c r="G19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I19" s="11"/>
+      <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9">
+      <c r="A20" s="2">
         <v>13</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="3">
         <v>46246</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G20" s="11" t="s">
+      <c r="G20" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I20" s="11"/>
+      <c r="I20" s="4"/>
     </row>
     <row r="21" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+      <c r="A21" s="2">
         <v>14</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="3">
         <v>46247</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E21" s="11" t="s">
+      <c r="E21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="11" t="s">
+      <c r="F21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="11" t="s">
+      <c r="G21" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="11"/>
+      <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="9">
+      <c r="A22" s="2">
         <v>15</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="3">
         <v>46248</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="E22" s="11" t="s">
+      <c r="E22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I22" s="11"/>
+      <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
+      <c r="A24" s="2">
         <v>16</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="3">
         <v>46251</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G24" s="11" t="s">
+      <c r="G24" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I24" s="11"/>
+      <c r="I24" s="4"/>
     </row>
     <row r="25" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
+      <c r="A25" s="2">
         <v>17</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="3">
         <v>46252</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I25" s="11"/>
+      <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
+      <c r="A26" s="2">
         <v>18</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="3">
         <v>46253</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I26" s="11"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
+      <c r="A27" s="2">
         <v>19</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="3">
         <v>46254</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I27" s="11"/>
+      <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
+      <c r="A28" s="2">
         <v>20</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="3">
         <v>46255</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="11"/>
+      <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
-      <c r="I29" s="5"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
     </row>
     <row r="30" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
+      <c r="A30" s="2">
         <v>21</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="3">
         <v>46258</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="E30" s="11" t="s">
+      <c r="E30" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="11" t="s">
+      <c r="F30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G30" s="11" t="s">
+      <c r="G30" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I30" s="11"/>
+      <c r="I30" s="4"/>
     </row>
     <row r="31" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="9">
+      <c r="A31" s="2">
         <v>22</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="3">
         <v>46259</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E31" s="11" t="s">
+      <c r="E31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="G31" s="11" t="s">
+      <c r="G31" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I31" s="11"/>
+      <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
+      <c r="A32" s="2">
         <v>23</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="3">
         <v>46260</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E32" s="11" t="s">
+      <c r="E32" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G32" s="11" t="s">
+      <c r="G32" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="H32" s="9" t="s">
+      <c r="H32" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I32" s="11"/>
+      <c r="I32" s="4"/>
     </row>
     <row r="33" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="9">
+      <c r="A33" s="2">
         <v>24</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="3">
         <v>46261</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="11" t="s">
+      <c r="E33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="11" t="s">
+      <c r="G33" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="H33" s="9" t="s">
+      <c r="H33" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I33" s="11"/>
+      <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="9">
+      <c r="A34" s="2">
         <v>25</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="3">
         <v>46262</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="D34" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E34" s="11" t="s">
+      <c r="E34" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G34" s="11" t="s">
+      <c r="G34" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I34" s="11"/>
+      <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
-      <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
-      <c r="I35" s="5"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
     </row>
     <row r="36" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+      <c r="A36" s="2">
         <v>26</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="3">
         <v>46265</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="D36" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="G36" s="11" t="s">
+      <c r="G36" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="H36" s="9" t="s">
+      <c r="H36" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="11"/>
+      <c r="I36" s="4"/>
     </row>
     <row r="37" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
+      <c r="A37" s="2">
         <v>27</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="3">
         <v>46266</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E37" s="11" t="s">
+      <c r="E37" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F37" s="11" t="s">
+      <c r="F37" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="G37" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I37" s="11"/>
+      <c r="I37" s="4"/>
     </row>
     <row r="38" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+      <c r="A38" s="2">
         <v>28</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="3">
         <v>46267</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="D38" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="E38" s="11" t="s">
+      <c r="E38" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G38" s="11" t="s">
+      <c r="G38" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="H38" s="9" t="s">
+      <c r="H38" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I38" s="11"/>
+      <c r="I38" s="4"/>
     </row>
     <row r="39" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
+      <c r="A39" s="2">
         <v>29</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="3">
         <v>46268</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D39" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="E39" s="11" t="s">
+      <c r="E39" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F39" s="11" t="s">
+      <c r="F39" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="G39" s="11" t="s">
+      <c r="G39" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="H39" s="9" t="s">
+      <c r="H39" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I39" s="11"/>
+      <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
+      <c r="A40" s="2">
         <v>30</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="3">
         <v>46269</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="D40" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="E40" s="11" t="s">
+      <c r="E40" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="G40" s="11" t="s">
+      <c r="G40" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I40" s="11"/>
+      <c r="I40" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2547,2032 +2565,2032 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
     </row>
     <row r="4" spans="1:15" ht="28" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="L4" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="M4" s="8" t="s">
+      <c r="M4" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="N4" s="8" t="s">
+      <c r="N4" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="O4" s="8" t="s">
+      <c r="O4" s="1" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12" t="s">
+      <c r="K5" s="5"/>
+      <c r="L5" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="O5" s="12" t="s">
+      <c r="O5" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
+      <c r="A6" s="2">
         <v>1</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="9">
+      <c r="A7" s="2">
         <v>2</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+      <c r="A8" s="2">
         <v>3</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
-      <c r="N8" s="13"/>
-      <c r="O8" s="13"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="O8" s="6"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="9">
+      <c r="A9" s="2">
         <v>4</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
+      <c r="A10" s="2">
         <v>5</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="O10" s="6"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A11" s="9">
+      <c r="A11" s="2">
         <v>6</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
+      <c r="A12" s="2">
         <v>7</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="6"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="9">
+      <c r="A13" s="2">
         <v>8</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13"/>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A14" s="9">
+      <c r="A14" s="2">
         <v>9</v>
       </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A15" s="9">
+      <c r="A15" s="2">
         <v>10</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="9">
+      <c r="A16" s="2">
         <v>11</v>
       </c>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="13"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="13"/>
-      <c r="M16" s="13"/>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="9">
+      <c r="A17" s="2">
         <v>12</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A18" s="9">
+      <c r="A18" s="2">
         <v>13</v>
       </c>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A19" s="9">
+      <c r="A19" s="2">
         <v>14</v>
       </c>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A20" s="9">
+      <c r="A20" s="2">
         <v>15</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A21" s="9">
+      <c r="A21" s="2">
         <v>16</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-      <c r="N21" s="13"/>
-      <c r="O21" s="13"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A22" s="9">
+      <c r="A22" s="2">
         <v>17</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
-      <c r="J22" s="13"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="13"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="13"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A23" s="9">
+      <c r="A23" s="2">
         <v>18</v>
       </c>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
-      <c r="J23" s="13"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="13"/>
-      <c r="M23" s="13"/>
-      <c r="N23" s="13"/>
-      <c r="O23" s="13"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A24" s="9">
+      <c r="A24" s="2">
         <v>19</v>
       </c>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A25" s="9">
+      <c r="A25" s="2">
         <v>20</v>
       </c>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="13"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A26" s="9">
+      <c r="A26" s="2">
         <v>21</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
-      <c r="M26" s="13"/>
-      <c r="N26" s="13"/>
-      <c r="O26" s="13"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A27" s="9">
+      <c r="A27" s="2">
         <v>22</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="13"/>
-      <c r="M27" s="13"/>
-      <c r="N27" s="13"/>
-      <c r="O27" s="13"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A28" s="9">
+      <c r="A28" s="2">
         <v>23</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
-      <c r="J28" s="13"/>
-      <c r="K28" s="13"/>
-      <c r="L28" s="13"/>
-      <c r="M28" s="13"/>
-      <c r="N28" s="13"/>
-      <c r="O28" s="13"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A29" s="9">
+      <c r="A29" s="2">
         <v>24</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A30" s="9">
+      <c r="A30" s="2">
         <v>25</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
-      <c r="L30" s="13"/>
-      <c r="M30" s="13"/>
-      <c r="N30" s="13"/>
-      <c r="O30" s="13"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A31" s="9">
+      <c r="A31" s="2">
         <v>26</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
-      <c r="K31" s="13"/>
-      <c r="L31" s="13"/>
-      <c r="M31" s="13"/>
-      <c r="N31" s="13"/>
-      <c r="O31" s="13"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A32" s="9">
+      <c r="A32" s="2">
         <v>27</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
-      <c r="K32" s="13"/>
-      <c r="L32" s="13"/>
-      <c r="M32" s="13"/>
-      <c r="N32" s="13"/>
-      <c r="O32" s="13"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A33" s="9">
+      <c r="A33" s="2">
         <v>28</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
-      <c r="K33" s="13"/>
-      <c r="L33" s="13"/>
-      <c r="M33" s="13"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="13"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A34" s="9">
+      <c r="A34" s="2">
         <v>29</v>
       </c>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="13"/>
-      <c r="M34" s="13"/>
-      <c r="N34" s="13"/>
-      <c r="O34" s="13"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A35" s="9">
+      <c r="A35" s="2">
         <v>30</v>
       </c>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A36" s="9">
+      <c r="A36" s="2">
         <v>31</v>
       </c>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
-      <c r="K36" s="13"/>
-      <c r="L36" s="13"/>
-      <c r="M36" s="13"/>
-      <c r="N36" s="13"/>
-      <c r="O36" s="13"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A37" s="9">
+      <c r="A37" s="2">
         <v>32</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
-      <c r="K37" s="13"/>
-      <c r="L37" s="13"/>
-      <c r="M37" s="13"/>
-      <c r="N37" s="13"/>
-      <c r="O37" s="13"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A38" s="9">
+      <c r="A38" s="2">
         <v>33</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-      <c r="N38" s="13"/>
-      <c r="O38" s="13"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A39" s="9">
+      <c r="A39" s="2">
         <v>34</v>
       </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-      <c r="L39" s="13"/>
-      <c r="M39" s="13"/>
-      <c r="N39" s="13"/>
-      <c r="O39" s="13"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A40" s="9">
+      <c r="A40" s="2">
         <v>35</v>
       </c>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="13"/>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-      <c r="L40" s="13"/>
-      <c r="M40" s="13"/>
-      <c r="N40" s="13"/>
-      <c r="O40" s="13"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A41" s="9">
+      <c r="A41" s="2">
         <v>36</v>
       </c>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="13"/>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-      <c r="L41" s="13"/>
-      <c r="M41" s="13"/>
-      <c r="N41" s="13"/>
-      <c r="O41" s="13"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A42" s="9">
+      <c r="A42" s="2">
         <v>37</v>
       </c>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="13"/>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-      <c r="L42" s="13"/>
-      <c r="M42" s="13"/>
-      <c r="N42" s="13"/>
-      <c r="O42" s="13"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A43" s="9">
+      <c r="A43" s="2">
         <v>38</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="13"/>
-      <c r="J43" s="13"/>
-      <c r="K43" s="13"/>
-      <c r="L43" s="13"/>
-      <c r="M43" s="13"/>
-      <c r="N43" s="13"/>
-      <c r="O43" s="13"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A44" s="9">
+      <c r="A44" s="2">
         <v>39</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="13"/>
-      <c r="J44" s="13"/>
-      <c r="K44" s="13"/>
-      <c r="L44" s="13"/>
-      <c r="M44" s="13"/>
-      <c r="N44" s="13"/>
-      <c r="O44" s="13"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A45" s="9">
+      <c r="A45" s="2">
         <v>40</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="13"/>
-      <c r="J45" s="13"/>
-      <c r="K45" s="13"/>
-      <c r="L45" s="13"/>
-      <c r="M45" s="13"/>
-      <c r="N45" s="13"/>
-      <c r="O45" s="13"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46" s="9">
+      <c r="A46" s="2">
         <v>41</v>
       </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="13"/>
-      <c r="J46" s="13"/>
-      <c r="K46" s="13"/>
-      <c r="L46" s="13"/>
-      <c r="M46" s="13"/>
-      <c r="N46" s="13"/>
-      <c r="O46" s="13"/>
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A47" s="9">
+      <c r="A47" s="2">
         <v>42</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="13"/>
-      <c r="J47" s="13"/>
-      <c r="K47" s="13"/>
-      <c r="L47" s="13"/>
-      <c r="M47" s="13"/>
-      <c r="N47" s="13"/>
-      <c r="O47" s="13"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48" s="9">
+      <c r="A48" s="2">
         <v>43</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="13"/>
-      <c r="J48" s="13"/>
-      <c r="K48" s="13"/>
-      <c r="L48" s="13"/>
-      <c r="M48" s="13"/>
-      <c r="N48" s="13"/>
-      <c r="O48" s="13"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6"/>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A49" s="9">
+      <c r="A49" s="2">
         <v>44</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="13"/>
-      <c r="J49" s="13"/>
-      <c r="K49" s="13"/>
-      <c r="L49" s="13"/>
-      <c r="M49" s="13"/>
-      <c r="N49" s="13"/>
-      <c r="O49" s="13"/>
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="6"/>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6"/>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A50" s="9">
+      <c r="A50" s="2">
         <v>45</v>
       </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="13"/>
+      <c r="B50" s="6"/>
+      <c r="C50" s="6"/>
+      <c r="D50" s="6"/>
+      <c r="E50" s="6"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A51" s="9">
+      <c r="A51" s="2">
         <v>46</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="H51" s="13"/>
-      <c r="I51" s="13"/>
-      <c r="J51" s="13"/>
-      <c r="K51" s="13"/>
-      <c r="L51" s="13"/>
-      <c r="M51" s="13"/>
-      <c r="N51" s="13"/>
-      <c r="O51" s="13"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A52" s="9">
+      <c r="A52" s="2">
         <v>47</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
+      <c r="B52" s="6"/>
+      <c r="C52" s="6"/>
+      <c r="D52" s="6"/>
+      <c r="E52" s="6"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6"/>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A53" s="9">
+      <c r="A53" s="2">
         <v>48</v>
       </c>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
-      <c r="H53" s="13"/>
-      <c r="I53" s="13"/>
-      <c r="J53" s="13"/>
-      <c r="K53" s="13"/>
-      <c r="L53" s="13"/>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
-      <c r="O53" s="13"/>
+      <c r="B53" s="6"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A54" s="9">
+      <c r="A54" s="2">
         <v>49</v>
       </c>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="13"/>
-      <c r="J54" s="13"/>
-      <c r="K54" s="13"/>
-      <c r="L54" s="13"/>
-      <c r="M54" s="13"/>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6"/>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A55" s="9">
+      <c r="A55" s="2">
         <v>50</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
-      <c r="M55" s="13"/>
-      <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="6"/>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6"/>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A56" s="9">
+      <c r="A56" s="2">
         <v>51</v>
       </c>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="13"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="13"/>
-      <c r="J56" s="13"/>
-      <c r="K56" s="13"/>
-      <c r="L56" s="13"/>
-      <c r="M56" s="13"/>
-      <c r="N56" s="13"/>
-      <c r="O56" s="13"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6"/>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6"/>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A57" s="9">
+      <c r="A57" s="2">
         <v>52</v>
       </c>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-      <c r="H57" s="13"/>
-      <c r="I57" s="13"/>
-      <c r="J57" s="13"/>
-      <c r="K57" s="13"/>
-      <c r="L57" s="13"/>
-      <c r="M57" s="13"/>
-      <c r="N57" s="13"/>
-      <c r="O57" s="13"/>
+      <c r="B57" s="6"/>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A58" s="9">
+      <c r="A58" s="2">
         <v>53</v>
       </c>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="13"/>
-      <c r="H58" s="13"/>
-      <c r="I58" s="13"/>
-      <c r="J58" s="13"/>
-      <c r="K58" s="13"/>
-      <c r="L58" s="13"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
+      <c r="B58" s="6"/>
+      <c r="C58" s="6"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A59" s="9">
+      <c r="A59" s="2">
         <v>54</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
-      <c r="H59" s="13"/>
-      <c r="I59" s="13"/>
-      <c r="J59" s="13"/>
-      <c r="K59" s="13"/>
-      <c r="L59" s="13"/>
-      <c r="M59" s="13"/>
-      <c r="N59" s="13"/>
-      <c r="O59" s="13"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6"/>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A60" s="9">
+      <c r="A60" s="2">
         <v>55</v>
       </c>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="13"/>
-      <c r="H60" s="13"/>
-      <c r="I60" s="13"/>
-      <c r="J60" s="13"/>
-      <c r="K60" s="13"/>
-      <c r="L60" s="13"/>
-      <c r="M60" s="13"/>
-      <c r="N60" s="13"/>
-      <c r="O60" s="13"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6"/>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A61" s="9">
+      <c r="A61" s="2">
         <v>56</v>
       </c>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="13"/>
-      <c r="H61" s="13"/>
-      <c r="I61" s="13"/>
-      <c r="J61" s="13"/>
-      <c r="K61" s="13"/>
-      <c r="L61" s="13"/>
-      <c r="M61" s="13"/>
-      <c r="N61" s="13"/>
-      <c r="O61" s="13"/>
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A62" s="9">
+      <c r="A62" s="2">
         <v>57</v>
       </c>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="13"/>
-      <c r="H62" s="13"/>
-      <c r="I62" s="13"/>
-      <c r="J62" s="13"/>
-      <c r="K62" s="13"/>
-      <c r="L62" s="13"/>
-      <c r="M62" s="13"/>
-      <c r="N62" s="13"/>
-      <c r="O62" s="13"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6"/>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A63" s="9">
+      <c r="A63" s="2">
         <v>58</v>
       </c>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="13"/>
-      <c r="H63" s="13"/>
-      <c r="I63" s="13"/>
-      <c r="J63" s="13"/>
-      <c r="K63" s="13"/>
-      <c r="L63" s="13"/>
-      <c r="M63" s="13"/>
-      <c r="N63" s="13"/>
-      <c r="O63" s="13"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="6"/>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6"/>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A64" s="9">
+      <c r="A64" s="2">
         <v>59</v>
       </c>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="13"/>
-      <c r="H64" s="13"/>
-      <c r="I64" s="13"/>
-      <c r="J64" s="13"/>
-      <c r="K64" s="13"/>
-      <c r="L64" s="13"/>
-      <c r="M64" s="13"/>
-      <c r="N64" s="13"/>
-      <c r="O64" s="13"/>
+      <c r="B64" s="6"/>
+      <c r="C64" s="6"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6"/>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A65" s="9">
+      <c r="A65" s="2">
         <v>60</v>
       </c>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="13"/>
-      <c r="J65" s="13"/>
-      <c r="K65" s="13"/>
-      <c r="L65" s="13"/>
-      <c r="M65" s="13"/>
-      <c r="N65" s="13"/>
-      <c r="O65" s="13"/>
+      <c r="B65" s="6"/>
+      <c r="C65" s="6"/>
+      <c r="D65" s="6"/>
+      <c r="E65" s="6"/>
+      <c r="F65" s="6"/>
+      <c r="G65" s="6"/>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A66" s="9">
+      <c r="A66" s="2">
         <v>61</v>
       </c>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="13"/>
-      <c r="J66" s="13"/>
-      <c r="K66" s="13"/>
-      <c r="L66" s="13"/>
-      <c r="M66" s="13"/>
-      <c r="N66" s="13"/>
-      <c r="O66" s="13"/>
+      <c r="B66" s="6"/>
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6"/>
+      <c r="O66" s="6"/>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A67" s="9">
+      <c r="A67" s="2">
         <v>62</v>
       </c>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="13"/>
-      <c r="J67" s="13"/>
-      <c r="K67" s="13"/>
-      <c r="L67" s="13"/>
-      <c r="M67" s="13"/>
-      <c r="N67" s="13"/>
-      <c r="O67" s="13"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A68" s="9">
+      <c r="A68" s="2">
         <v>63</v>
       </c>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="13"/>
-      <c r="J68" s="13"/>
-      <c r="K68" s="13"/>
-      <c r="L68" s="13"/>
-      <c r="M68" s="13"/>
-      <c r="N68" s="13"/>
-      <c r="O68" s="13"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A69" s="9">
+      <c r="A69" s="2">
         <v>64</v>
       </c>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="13"/>
-      <c r="J69" s="13"/>
-      <c r="K69" s="13"/>
-      <c r="L69" s="13"/>
-      <c r="M69" s="13"/>
-      <c r="N69" s="13"/>
-      <c r="O69" s="13"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A70" s="9">
+      <c r="A70" s="2">
         <v>65</v>
       </c>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="13"/>
-      <c r="J70" s="13"/>
-      <c r="K70" s="13"/>
-      <c r="L70" s="13"/>
-      <c r="M70" s="13"/>
-      <c r="N70" s="13"/>
-      <c r="O70" s="13"/>
+      <c r="B70" s="6"/>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="6"/>
+      <c r="F70" s="6"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6"/>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A71" s="9">
+      <c r="A71" s="2">
         <v>66</v>
       </c>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="13"/>
-      <c r="J71" s="13"/>
-      <c r="K71" s="13"/>
-      <c r="L71" s="13"/>
-      <c r="M71" s="13"/>
-      <c r="N71" s="13"/>
-      <c r="O71" s="13"/>
+      <c r="B71" s="6"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6"/>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A72" s="9">
+      <c r="A72" s="2">
         <v>67</v>
       </c>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="13"/>
-      <c r="J72" s="13"/>
-      <c r="K72" s="13"/>
-      <c r="L72" s="13"/>
-      <c r="M72" s="13"/>
-      <c r="N72" s="13"/>
-      <c r="O72" s="13"/>
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="6"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A73" s="9">
+      <c r="A73" s="2">
         <v>68</v>
       </c>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="13"/>
-      <c r="J73" s="13"/>
-      <c r="K73" s="13"/>
-      <c r="L73" s="13"/>
-      <c r="M73" s="13"/>
-      <c r="N73" s="13"/>
-      <c r="O73" s="13"/>
+      <c r="B73" s="6"/>
+      <c r="C73" s="6"/>
+      <c r="D73" s="6"/>
+      <c r="E73" s="6"/>
+      <c r="F73" s="6"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A74" s="9">
+      <c r="A74" s="2">
         <v>69</v>
       </c>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="13"/>
-      <c r="J74" s="13"/>
-      <c r="K74" s="13"/>
-      <c r="L74" s="13"/>
-      <c r="M74" s="13"/>
-      <c r="N74" s="13"/>
-      <c r="O74" s="13"/>
+      <c r="B74" s="6"/>
+      <c r="C74" s="6"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="6"/>
+      <c r="F74" s="6"/>
+      <c r="G74" s="6"/>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" s="6"/>
+      <c r="K74" s="6"/>
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A75" s="9">
+      <c r="A75" s="2">
         <v>70</v>
       </c>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="13"/>
-      <c r="J75" s="13"/>
-      <c r="K75" s="13"/>
-      <c r="L75" s="13"/>
-      <c r="M75" s="13"/>
-      <c r="N75" s="13"/>
-      <c r="O75" s="13"/>
+      <c r="B75" s="6"/>
+      <c r="C75" s="6"/>
+      <c r="D75" s="6"/>
+      <c r="E75" s="6"/>
+      <c r="F75" s="6"/>
+      <c r="G75" s="6"/>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" s="6"/>
+      <c r="K75" s="6"/>
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A76" s="9">
+      <c r="A76" s="2">
         <v>71</v>
       </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="13"/>
-      <c r="J76" s="13"/>
-      <c r="K76" s="13"/>
-      <c r="L76" s="13"/>
-      <c r="M76" s="13"/>
-      <c r="N76" s="13"/>
-      <c r="O76" s="13"/>
+      <c r="B76" s="6"/>
+      <c r="C76" s="6"/>
+      <c r="D76" s="6"/>
+      <c r="E76" s="6"/>
+      <c r="F76" s="6"/>
+      <c r="G76" s="6"/>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6"/>
+      <c r="K76" s="6"/>
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A77" s="9">
+      <c r="A77" s="2">
         <v>72</v>
       </c>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="13"/>
-      <c r="J77" s="13"/>
-      <c r="K77" s="13"/>
-      <c r="L77" s="13"/>
-      <c r="M77" s="13"/>
-      <c r="N77" s="13"/>
-      <c r="O77" s="13"/>
+      <c r="B77" s="6"/>
+      <c r="C77" s="6"/>
+      <c r="D77" s="6"/>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6"/>
+      <c r="G77" s="6"/>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" s="6"/>
+      <c r="K77" s="6"/>
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A78" s="9">
+      <c r="A78" s="2">
         <v>73</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="13"/>
-      <c r="J78" s="13"/>
-      <c r="K78" s="13"/>
-      <c r="L78" s="13"/>
-      <c r="M78" s="13"/>
-      <c r="N78" s="13"/>
-      <c r="O78" s="13"/>
+      <c r="B78" s="6"/>
+      <c r="C78" s="6"/>
+      <c r="D78" s="6"/>
+      <c r="E78" s="6"/>
+      <c r="F78" s="6"/>
+      <c r="G78" s="6"/>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" s="6"/>
+      <c r="K78" s="6"/>
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A79" s="9">
+      <c r="A79" s="2">
         <v>74</v>
       </c>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="13"/>
-      <c r="J79" s="13"/>
-      <c r="K79" s="13"/>
-      <c r="L79" s="13"/>
-      <c r="M79" s="13"/>
-      <c r="N79" s="13"/>
-      <c r="O79" s="13"/>
+      <c r="B79" s="6"/>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6"/>
+      <c r="G79" s="6"/>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" s="6"/>
+      <c r="K79" s="6"/>
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A80" s="9">
+      <c r="A80" s="2">
         <v>75</v>
       </c>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="13"/>
-      <c r="J80" s="13"/>
-      <c r="K80" s="13"/>
-      <c r="L80" s="13"/>
-      <c r="M80" s="13"/>
-      <c r="N80" s="13"/>
-      <c r="O80" s="13"/>
+      <c r="B80" s="6"/>
+      <c r="C80" s="6"/>
+      <c r="D80" s="6"/>
+      <c r="E80" s="6"/>
+      <c r="F80" s="6"/>
+      <c r="G80" s="6"/>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6"/>
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A81" s="9">
+      <c r="A81" s="2">
         <v>76</v>
       </c>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="13"/>
-      <c r="J81" s="13"/>
-      <c r="K81" s="13"/>
-      <c r="L81" s="13"/>
-      <c r="M81" s="13"/>
-      <c r="N81" s="13"/>
-      <c r="O81" s="13"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="6"/>
+      <c r="D81" s="6"/>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6"/>
+      <c r="G81" s="6"/>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" s="6"/>
+      <c r="K81" s="6"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A82" s="9">
+      <c r="A82" s="2">
         <v>77</v>
       </c>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="13"/>
-      <c r="H82" s="13"/>
-      <c r="I82" s="13"/>
-      <c r="J82" s="13"/>
-      <c r="K82" s="13"/>
-      <c r="L82" s="13"/>
-      <c r="M82" s="13"/>
-      <c r="N82" s="13"/>
-      <c r="O82" s="13"/>
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+      <c r="F82" s="6"/>
+      <c r="G82" s="6"/>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" s="6"/>
+      <c r="K82" s="6"/>
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="6"/>
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A83" s="9">
+      <c r="A83" s="2">
         <v>78</v>
       </c>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="13"/>
-      <c r="H83" s="13"/>
-      <c r="I83" s="13"/>
-      <c r="J83" s="13"/>
-      <c r="K83" s="13"/>
-      <c r="L83" s="13"/>
-      <c r="M83" s="13"/>
-      <c r="N83" s="13"/>
-      <c r="O83" s="13"/>
+      <c r="B83" s="6"/>
+      <c r="C83" s="6"/>
+      <c r="D83" s="6"/>
+      <c r="E83" s="6"/>
+      <c r="F83" s="6"/>
+      <c r="G83" s="6"/>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" s="6"/>
+      <c r="K83" s="6"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A84" s="9">
+      <c r="A84" s="2">
         <v>79</v>
       </c>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="13"/>
-      <c r="H84" s="13"/>
-      <c r="I84" s="13"/>
-      <c r="J84" s="13"/>
-      <c r="K84" s="13"/>
-      <c r="L84" s="13"/>
-      <c r="M84" s="13"/>
-      <c r="N84" s="13"/>
-      <c r="O84" s="13"/>
+      <c r="B84" s="6"/>
+      <c r="C84" s="6"/>
+      <c r="D84" s="6"/>
+      <c r="E84" s="6"/>
+      <c r="F84" s="6"/>
+      <c r="G84" s="6"/>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" s="6"/>
+      <c r="K84" s="6"/>
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A85" s="9">
+      <c r="A85" s="2">
         <v>80</v>
       </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="13"/>
-      <c r="H85" s="13"/>
-      <c r="I85" s="13"/>
-      <c r="J85" s="13"/>
-      <c r="K85" s="13"/>
-      <c r="L85" s="13"/>
-      <c r="M85" s="13"/>
-      <c r="N85" s="13"/>
-      <c r="O85" s="13"/>
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6"/>
+      <c r="E85" s="6"/>
+      <c r="F85" s="6"/>
+      <c r="G85" s="6"/>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" s="6"/>
+      <c r="K85" s="6"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A86" s="9">
+      <c r="A86" s="2">
         <v>81</v>
       </c>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="13"/>
-      <c r="H86" s="13"/>
-      <c r="I86" s="13"/>
-      <c r="J86" s="13"/>
-      <c r="K86" s="13"/>
-      <c r="L86" s="13"/>
-      <c r="M86" s="13"/>
-      <c r="N86" s="13"/>
-      <c r="O86" s="13"/>
+      <c r="B86" s="6"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="6"/>
+      <c r="E86" s="6"/>
+      <c r="F86" s="6"/>
+      <c r="G86" s="6"/>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" s="6"/>
+      <c r="K86" s="6"/>
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A87" s="9">
+      <c r="A87" s="2">
         <v>82</v>
       </c>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="13"/>
-      <c r="H87" s="13"/>
-      <c r="I87" s="13"/>
-      <c r="J87" s="13"/>
-      <c r="K87" s="13"/>
-      <c r="L87" s="13"/>
-      <c r="M87" s="13"/>
-      <c r="N87" s="13"/>
-      <c r="O87" s="13"/>
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="6"/>
+      <c r="F87" s="6"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" s="6"/>
+      <c r="K87" s="6"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A88" s="9">
+      <c r="A88" s="2">
         <v>83</v>
       </c>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="13"/>
-      <c r="H88" s="13"/>
-      <c r="I88" s="13"/>
-      <c r="J88" s="13"/>
-      <c r="K88" s="13"/>
-      <c r="L88" s="13"/>
-      <c r="M88" s="13"/>
-      <c r="N88" s="13"/>
-      <c r="O88" s="13"/>
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="6"/>
+      <c r="F88" s="6"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6"/>
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A89" s="9">
+      <c r="A89" s="2">
         <v>84</v>
       </c>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="13"/>
-      <c r="H89" s="13"/>
-      <c r="I89" s="13"/>
-      <c r="J89" s="13"/>
-      <c r="K89" s="13"/>
-      <c r="L89" s="13"/>
-      <c r="M89" s="13"/>
-      <c r="N89" s="13"/>
-      <c r="O89" s="13"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="E89" s="6"/>
+      <c r="F89" s="6"/>
+      <c r="G89" s="6"/>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6"/>
+      <c r="K89" s="6"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A90" s="9">
+      <c r="A90" s="2">
         <v>85</v>
       </c>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="13"/>
-      <c r="H90" s="13"/>
-      <c r="I90" s="13"/>
-      <c r="J90" s="13"/>
-      <c r="K90" s="13"/>
-      <c r="L90" s="13"/>
-      <c r="M90" s="13"/>
-      <c r="N90" s="13"/>
-      <c r="O90" s="13"/>
+      <c r="B90" s="6"/>
+      <c r="C90" s="6"/>
+      <c r="D90" s="6"/>
+      <c r="E90" s="6"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="6"/>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6"/>
+      <c r="K90" s="6"/>
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A91" s="9">
+      <c r="A91" s="2">
         <v>86</v>
       </c>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="13"/>
-      <c r="H91" s="13"/>
-      <c r="I91" s="13"/>
-      <c r="J91" s="13"/>
-      <c r="K91" s="13"/>
-      <c r="L91" s="13"/>
-      <c r="M91" s="13"/>
-      <c r="N91" s="13"/>
-      <c r="O91" s="13"/>
+      <c r="B91" s="6"/>
+      <c r="C91" s="6"/>
+      <c r="D91" s="6"/>
+      <c r="E91" s="6"/>
+      <c r="F91" s="6"/>
+      <c r="G91" s="6"/>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6"/>
+      <c r="K91" s="6"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A92" s="9">
+      <c r="A92" s="2">
         <v>87</v>
       </c>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="13"/>
-      <c r="H92" s="13"/>
-      <c r="I92" s="13"/>
-      <c r="J92" s="13"/>
-      <c r="K92" s="13"/>
-      <c r="L92" s="13"/>
-      <c r="M92" s="13"/>
-      <c r="N92" s="13"/>
-      <c r="O92" s="13"/>
+      <c r="B92" s="6"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="E92" s="6"/>
+      <c r="F92" s="6"/>
+      <c r="G92" s="6"/>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6"/>
+      <c r="K92" s="6"/>
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A93" s="9">
+      <c r="A93" s="2">
         <v>88</v>
       </c>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="13"/>
-      <c r="H93" s="13"/>
-      <c r="I93" s="13"/>
-      <c r="J93" s="13"/>
-      <c r="K93" s="13"/>
-      <c r="L93" s="13"/>
-      <c r="M93" s="13"/>
-      <c r="N93" s="13"/>
-      <c r="O93" s="13"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="6"/>
+      <c r="D93" s="6"/>
+      <c r="E93" s="6"/>
+      <c r="F93" s="6"/>
+      <c r="G93" s="6"/>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" s="6"/>
+      <c r="K93" s="6"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A94" s="9">
+      <c r="A94" s="2">
         <v>89</v>
       </c>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="13"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="13"/>
-      <c r="J94" s="13"/>
-      <c r="K94" s="13"/>
-      <c r="L94" s="13"/>
-      <c r="M94" s="13"/>
-      <c r="N94" s="13"/>
-      <c r="O94" s="13"/>
+      <c r="B94" s="6"/>
+      <c r="C94" s="6"/>
+      <c r="D94" s="6"/>
+      <c r="E94" s="6"/>
+      <c r="F94" s="6"/>
+      <c r="G94" s="6"/>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" s="6"/>
+      <c r="K94" s="6"/>
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A95" s="9">
+      <c r="A95" s="2">
         <v>90</v>
       </c>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="13"/>
-      <c r="H95" s="13"/>
-      <c r="I95" s="13"/>
-      <c r="J95" s="13"/>
-      <c r="K95" s="13"/>
-      <c r="L95" s="13"/>
-      <c r="M95" s="13"/>
-      <c r="N95" s="13"/>
-      <c r="O95" s="13"/>
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6"/>
+      <c r="E95" s="6"/>
+      <c r="F95" s="6"/>
+      <c r="G95" s="6"/>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" s="6"/>
+      <c r="K95" s="6"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A96" s="9">
+      <c r="A96" s="2">
         <v>91</v>
       </c>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="13"/>
-      <c r="H96" s="13"/>
-      <c r="I96" s="13"/>
-      <c r="J96" s="13"/>
-      <c r="K96" s="13"/>
-      <c r="L96" s="13"/>
-      <c r="M96" s="13"/>
-      <c r="N96" s="13"/>
-      <c r="O96" s="13"/>
+      <c r="B96" s="6"/>
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+      <c r="E96" s="6"/>
+      <c r="F96" s="6"/>
+      <c r="G96" s="6"/>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
+      <c r="K96" s="6"/>
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="6"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A97" s="9">
+      <c r="A97" s="2">
         <v>92</v>
       </c>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="13"/>
-      <c r="H97" s="13"/>
-      <c r="I97" s="13"/>
-      <c r="J97" s="13"/>
-      <c r="K97" s="13"/>
-      <c r="L97" s="13"/>
-      <c r="M97" s="13"/>
-      <c r="N97" s="13"/>
-      <c r="O97" s="13"/>
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="6"/>
+      <c r="F97" s="6"/>
+      <c r="G97" s="6"/>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6"/>
+      <c r="K97" s="6"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A98" s="9">
+      <c r="A98" s="2">
         <v>93</v>
       </c>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="13"/>
-      <c r="H98" s="13"/>
-      <c r="I98" s="13"/>
-      <c r="J98" s="13"/>
-      <c r="K98" s="13"/>
-      <c r="L98" s="13"/>
-      <c r="M98" s="13"/>
-      <c r="N98" s="13"/>
-      <c r="O98" s="13"/>
+      <c r="B98" s="6"/>
+      <c r="C98" s="6"/>
+      <c r="D98" s="6"/>
+      <c r="E98" s="6"/>
+      <c r="F98" s="6"/>
+      <c r="G98" s="6"/>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" s="6"/>
+      <c r="K98" s="6"/>
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A99" s="9">
+      <c r="A99" s="2">
         <v>94</v>
       </c>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="13"/>
-      <c r="H99" s="13"/>
-      <c r="I99" s="13"/>
-      <c r="J99" s="13"/>
-      <c r="K99" s="13"/>
-      <c r="L99" s="13"/>
-      <c r="M99" s="13"/>
-      <c r="N99" s="13"/>
-      <c r="O99" s="13"/>
+      <c r="B99" s="6"/>
+      <c r="C99" s="6"/>
+      <c r="D99" s="6"/>
+      <c r="E99" s="6"/>
+      <c r="F99" s="6"/>
+      <c r="G99" s="6"/>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6"/>
+      <c r="K99" s="6"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="6"/>
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A100" s="9">
+      <c r="A100" s="2">
         <v>95</v>
       </c>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="13"/>
-      <c r="H100" s="13"/>
-      <c r="I100" s="13"/>
-      <c r="J100" s="13"/>
-      <c r="K100" s="13"/>
-      <c r="L100" s="13"/>
-      <c r="M100" s="13"/>
-      <c r="N100" s="13"/>
-      <c r="O100" s="13"/>
+      <c r="B100" s="6"/>
+      <c r="C100" s="6"/>
+      <c r="D100" s="6"/>
+      <c r="E100" s="6"/>
+      <c r="F100" s="6"/>
+      <c r="G100" s="6"/>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" s="6"/>
+      <c r="K100" s="6"/>
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A101" s="9">
+      <c r="A101" s="2">
         <v>96</v>
       </c>
-      <c r="B101" s="13"/>
-      <c r="C101" s="13"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="13"/>
-      <c r="H101" s="13"/>
-      <c r="I101" s="13"/>
-      <c r="J101" s="13"/>
-      <c r="K101" s="13"/>
-      <c r="L101" s="13"/>
-      <c r="M101" s="13"/>
-      <c r="N101" s="13"/>
-      <c r="O101" s="13"/>
+      <c r="B101" s="6"/>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="6"/>
+      <c r="O101" s="6"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A102" s="9">
+      <c r="A102" s="2">
         <v>97</v>
       </c>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="13"/>
-      <c r="H102" s="13"/>
-      <c r="I102" s="13"/>
-      <c r="J102" s="13"/>
-      <c r="K102" s="13"/>
-      <c r="L102" s="13"/>
-      <c r="M102" s="13"/>
-      <c r="N102" s="13"/>
-      <c r="O102" s="13"/>
+      <c r="B102" s="6"/>
+      <c r="C102" s="6"/>
+      <c r="D102" s="6"/>
+      <c r="E102" s="6"/>
+      <c r="F102" s="6"/>
+      <c r="G102" s="6"/>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6"/>
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="6"/>
+      <c r="O102" s="6"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A103" s="9">
+      <c r="A103" s="2">
         <v>98</v>
       </c>
-      <c r="B103" s="13"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="13"/>
-      <c r="H103" s="13"/>
-      <c r="I103" s="13"/>
-      <c r="J103" s="13"/>
-      <c r="K103" s="13"/>
-      <c r="L103" s="13"/>
-      <c r="M103" s="13"/>
-      <c r="N103" s="13"/>
-      <c r="O103" s="13"/>
+      <c r="B103" s="6"/>
+      <c r="C103" s="6"/>
+      <c r="D103" s="6"/>
+      <c r="E103" s="6"/>
+      <c r="F103" s="6"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="6"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6"/>
+      <c r="K103" s="6"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
+      <c r="O103" s="6"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A104" s="9">
+      <c r="A104" s="2">
         <v>99</v>
       </c>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="13"/>
-      <c r="H104" s="13"/>
-      <c r="I104" s="13"/>
-      <c r="J104" s="13"/>
-      <c r="K104" s="13"/>
-      <c r="L104" s="13"/>
-      <c r="M104" s="13"/>
-      <c r="N104" s="13"/>
-      <c r="O104" s="13"/>
+      <c r="B104" s="6"/>
+      <c r="C104" s="6"/>
+      <c r="D104" s="6"/>
+      <c r="E104" s="6"/>
+      <c r="F104" s="6"/>
+      <c r="G104" s="6"/>
+      <c r="H104" s="6"/>
+      <c r="I104" s="6"/>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+      <c r="O104" s="6"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A105" s="9">
+      <c r="A105" s="2">
         <v>100</v>
       </c>
-      <c r="B105" s="13"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="13"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="13"/>
-      <c r="J105" s="13"/>
-      <c r="K105" s="13"/>
-      <c r="L105" s="13"/>
-      <c r="M105" s="13"/>
-      <c r="N105" s="13"/>
-      <c r="O105" s="13"/>
+      <c r="B105" s="6"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="6"/>
+      <c r="E105" s="6"/>
+      <c r="F105" s="6"/>
+      <c r="G105" s="6"/>
+      <c r="H105" s="6"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6"/>
+      <c r="K105" s="6"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
+      <c r="O105" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4608,110 +4626,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="15"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="14"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="4" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="4" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="14"/>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="4" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="14"/>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="4" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="4" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="14"/>
     </row>
     <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="4" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="4" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="14"/>
     </row>
     <row r="21" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="4" t="s">
         <v>198</v>
       </c>
     </row>
@@ -4742,345 +4760,345 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="15" t="s">
+      <c r="C5" s="9"/>
+      <c r="D5" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="8" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="B47" s="4"/>
-      <c r="D47" s="4" t="s">
+      <c r="B47" s="17"/>
+      <c r="D47" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="E47" s="4"/>
+      <c r="E47" s="17"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="B48" s="3"/>
-      <c r="D48" s="3" t="s">
+      <c r="B48" s="18"/>
+      <c r="D48" s="18" t="s">
         <v>210</v>
       </c>
-      <c r="E48" s="3"/>
+      <c r="E48" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5105,359 +5123,359 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="1" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="17">
-        <v>0</v>
-      </c>
-      <c r="C4" s="17">
-        <v>0</v>
-      </c>
-      <c r="D4" s="17">
-        <v>0</v>
-      </c>
-      <c r="E4" s="17">
-        <v>0</v>
-      </c>
-      <c r="F4" s="17">
-        <v>0</v>
-      </c>
-      <c r="G4" s="17">
-        <v>0</v>
-      </c>
-      <c r="H4" s="13">
+      <c r="B4" s="10">
+        <v>0</v>
+      </c>
+      <c r="C4" s="10">
+        <v>0</v>
+      </c>
+      <c r="D4" s="10">
+        <v>0</v>
+      </c>
+      <c r="E4" s="10">
+        <v>0</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
         <f t="shared" ref="H4:H13" si="0">SUM(B4:G4)</f>
         <v>0</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="6">
         <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B5" s="19">
-        <v>0</v>
-      </c>
-      <c r="C5" s="19">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19">
-        <v>0</v>
-      </c>
-      <c r="E5" s="19">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19">
-        <v>0</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0</v>
-      </c>
-      <c r="H5" s="18">
+      <c r="B5" s="12">
+        <v>0</v>
+      </c>
+      <c r="C5" s="12">
+        <v>0</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0</v>
+      </c>
+      <c r="H5" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="11">
         <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B6" s="17">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
-      </c>
-      <c r="D6" s="17">
-        <v>0</v>
-      </c>
-      <c r="E6" s="17">
-        <v>0</v>
-      </c>
-      <c r="F6" s="17">
-        <v>0</v>
-      </c>
-      <c r="G6" s="17">
-        <v>0</v>
-      </c>
-      <c r="H6" s="13">
+      <c r="B6" s="10">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10">
+        <v>0</v>
+      </c>
+      <c r="E6" s="10">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="6">
         <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="19">
-        <v>0</v>
-      </c>
-      <c r="C7" s="19">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19">
-        <v>0</v>
-      </c>
-      <c r="E7" s="19">
-        <v>0</v>
-      </c>
-      <c r="F7" s="19">
-        <v>0</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0</v>
-      </c>
-      <c r="H7" s="18">
+      <c r="B7" s="12">
+        <v>0</v>
+      </c>
+      <c r="C7" s="12">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0</v>
+      </c>
+      <c r="H7" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I7" s="18">
+      <c r="I7" s="11">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="17">
-        <v>0</v>
-      </c>
-      <c r="C8" s="17">
-        <v>0</v>
-      </c>
-      <c r="D8" s="17">
-        <v>0</v>
-      </c>
-      <c r="E8" s="17">
-        <v>0</v>
-      </c>
-      <c r="F8" s="17">
-        <v>0</v>
-      </c>
-      <c r="G8" s="17">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13">
+      <c r="B8" s="10">
+        <v>0</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="6">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B9" s="19">
-        <v>0</v>
-      </c>
-      <c r="C9" s="19">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19">
-        <v>0</v>
-      </c>
-      <c r="E9" s="19">
-        <v>0</v>
-      </c>
-      <c r="F9" s="19">
-        <v>0</v>
-      </c>
-      <c r="G9" s="19">
-        <v>0</v>
-      </c>
-      <c r="H9" s="18">
+      <c r="B9" s="12">
+        <v>0</v>
+      </c>
+      <c r="C9" s="12">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0</v>
+      </c>
+      <c r="H9" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I9" s="18">
+      <c r="I9" s="11">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="B10" s="17">
-        <v>0</v>
-      </c>
-      <c r="C10" s="17">
-        <v>0</v>
-      </c>
-      <c r="D10" s="17">
-        <v>0</v>
-      </c>
-      <c r="E10" s="17">
-        <v>0</v>
-      </c>
-      <c r="F10" s="17">
-        <v>0</v>
-      </c>
-      <c r="G10" s="17">
-        <v>0</v>
-      </c>
-      <c r="H10" s="13">
+      <c r="B10" s="10">
+        <v>0</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10">
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="19">
-        <v>0</v>
-      </c>
-      <c r="C11" s="19">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19">
-        <v>0</v>
-      </c>
-      <c r="E11" s="19">
-        <v>0</v>
-      </c>
-      <c r="F11" s="19">
-        <v>0</v>
-      </c>
-      <c r="G11" s="19">
-        <v>0</v>
-      </c>
-      <c r="H11" s="18">
+      <c r="B11" s="12">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12">
+        <v>0</v>
+      </c>
+      <c r="H11" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="11">
         <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="B12" s="17">
-        <v>0</v>
-      </c>
-      <c r="C12" s="17">
-        <v>0</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="13">
+      <c r="B12" s="10">
+        <v>0</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="6">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="19">
-        <v>0</v>
-      </c>
-      <c r="C13" s="19">
-        <v>0</v>
-      </c>
-      <c r="D13" s="19">
-        <v>0</v>
-      </c>
-      <c r="E13" s="19">
-        <v>0</v>
-      </c>
-      <c r="F13" s="19">
-        <v>0</v>
-      </c>
-      <c r="G13" s="19">
-        <v>0</v>
-      </c>
-      <c r="H13" s="18">
+      <c r="B13" s="12">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0</v>
+      </c>
+      <c r="H13" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="11">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5482,197 +5500,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="4" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="F5" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="13" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="20" t="s">
+      <c r="A7" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="13" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="13" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="E8" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="D9" s="20" t="s">
+      <c r="D9" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="G9" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="4" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5696,65 +5714,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C5" s="13"/>
+      <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C6" s="13"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="13"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="C8" s="13"/>
+      <c r="C8" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5777,233 +5795,233 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="8" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="13"/>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="13"/>
-      <c r="C16" s="13"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="13"/>
-      <c r="C18" s="13"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="13"/>
-      <c r="C19" s="13"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="13"/>
-      <c r="C23" s="13"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="13"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="13"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="13"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="13"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="13"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="13"/>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
+      <c r="A40" s="6"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="13"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
+      <c r="A41" s="6"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="13"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
+      <c r="A42" s="6"/>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6016,7 +6034,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -6334,6 +6352,46 @@
         <v>338</v>
       </c>
     </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>357</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/sendcleared-outreach-tracker.xlsx
+++ b/sendcleared-outreach-tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/timothyarmstead/Sendcleared/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F41755-2DE4-5245-9C60-23B55D1F12AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F286FE8-CFB2-3F45-92DB-92542E1BF411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6640" yWindow="2320" windowWidth="29900" windowHeight="17100" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="1260" windowWidth="22400" windowHeight="16220" tabRatio="500" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily Playbook" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,10 @@
     <sheet name="LinkedIn Requests" sheetId="4" r:id="rId4"/>
     <sheet name="Weekly Scoreboard" sheetId="5" r:id="rId5"/>
     <sheet name="Channel Strategy" sheetId="6" r:id="rId6"/>
-    <sheet name="Community Questions" sheetId="7" r:id="rId7"/>
-    <sheet name="Community Posts" sheetId="8" r:id="rId8"/>
-    <sheet name="Contacts " sheetId="9" r:id="rId9"/>
+    <sheet name="Linked in Content Plan" sheetId="10" r:id="rId7"/>
+    <sheet name="Community Questions" sheetId="7" r:id="rId8"/>
+    <sheet name="Community Posts" sheetId="8" r:id="rId9"/>
+    <sheet name="Contacts " sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="670">
   <si>
     <t>SendCleared — Daily Outreach Playbook  |  1 Hour / Day</t>
   </si>
@@ -581,9 +582,6 @@
   </si>
   <si>
     <t>Freelancer segment</t>
-  </si>
-  <si>
-    <t>Hi [Name], I'm building SendCleared — a tool that runs a pre-send QA check and gets client sign-off on every email campaign, whatever ESP you use. Would love to connect with other email freelancers.</t>
   </si>
   <si>
     <t>Agency segment</t>
@@ -634,15 +632,6 @@
   </si>
   <si>
     <t>Email body</t>
-  </si>
-  <si>
-    <t>Hi [Name],
-I'm the founder of SendCleared (sendcleared.com) — it runs a QA check on every email campaign and gets client sign-off through a single branded link, regardless of which ESP you use.
-I thought this might save your account managers the back-and-forth of chasing approval over Slack or email threads.
-I'd love to give your agency free access to try it — no credit card, no commitment.
-Would that be useful? Happy to jump on a 10-minute call too.
-Best,
-[Your name]</t>
   </si>
   <si>
     <t>COMMUNITY ANSWER TEMPLATE (Reddit / Indie Hackers / Slack)</t>
@@ -973,9 +962,6 @@
     <t>https://www.linkedin.com/in/nils-g-08583421a/</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/katarzynagolubinska/</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/ali-hassan-6aa1571ba/</t>
   </si>
   <si>
@@ -1003,9 +989,6 @@
     <t>https://www.linkedin.com/in/rhysalanharris/</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/kade-mcconville/</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/jack-squire/</t>
   </si>
   <si>
@@ -1027,9 +1010,6 @@
     <t>https://www.linkedin.com/in/haseeb-ahmedd/</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/markus-kovger-88b893272/</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/antony-newbold-hazebrooke-copywriting/</t>
   </si>
   <si>
@@ -1099,15 +1079,9 @@
     <t>https://www.linkedin.com/in/rachel-j-79296b129/</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/kevinsteba/</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/oviakpojotor/</t>
   </si>
   <si>
-    <t>https://www.linkedin.com/in/emmett-vonschreiber/</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/in/williamconsult/</t>
   </si>
   <si>
@@ -1133,6 +1107,1014 @@
   </si>
   <si>
     <t>https://www.linkedin.com/in/louise-rebecca-thomas/</t>
+  </si>
+  <si>
+    <t>SendCleared — Outreach Emails &amp; Follow-Up Sequence</t>
+  </si>
+  <si>
+    <t>Copy, personalise the [bracketed] fields, and send. Timing shown is days after the previous email if no reply.</t>
+  </si>
+  <si>
+    <t>FREELANCER SEGMENT</t>
+  </si>
+  <si>
+    <t>AGENCY SEGMENT</t>
+  </si>
+  <si>
+    <t>EMAIL 1 — INITIAL OUTREACH (Day 0)</t>
+  </si>
+  <si>
+    <t>A) "Quick one re: client sign-off on your campaigns"
+B) "Ever had a client dispute what they approved?"
+C) "A cleaner way to get client sign-off"</t>
+  </si>
+  <si>
+    <t>A) "A single approval link for every campaign, any ESP"
+B) "Stop chasing client sign-off over Slack"
+C) "Pre-send QA + client approval, in one step"</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+I'm the founder of SendCleared (sendcleared.com) — it runs a QA check on every email campaign and gets client sign-off through a single branded link, regardless of which ESP you use.
+I thought this might save your account managers the back-and-forth of chasing approval over Slack or email threads — especially if you're running campaigns across more than one ESP.
+I'd love to give your agency free access to try it — no credit card, no commitment. Would that be useful? Happy to jump on a 10-minute call too.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>EMAIL 2 — FOLLOW-UP 1 (Day +4, if no reply)</t>
+  </si>
+  <si>
+    <t>Subject line</t>
+  </si>
+  <si>
+    <t>Re: Quick one re: client sign-off on your campaigns</t>
+  </si>
+  <si>
+    <t>Re: A single approval link for every campaign, any ESP</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Following up on my note below — happy to set your agency up with free access to SendCleared, no strings attached. Takes a few minutes to add your first client.
+Let me know if it's useful, or if now's just not the right time.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>EMAIL 3 — FOLLOW-UP 2 / FINAL NUDGE (Day +10, if no reply)</t>
+  </si>
+  <si>
+    <t>Last note from me on this</t>
+  </si>
+  <si>
+    <t>One last thought, then I'll leave it there</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Last message from me on this one — if pre-send QA or client sign-off is ever a headache, SendCleared is there whenever it's useful: sendcleared.com.
+Happy to answer any questions any time, no follow-up needed from you.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Last note from me — if client approval or juggling QA across ESPs ever becomes a pain point, SendCleared is there: sendcleared.com. Free to try whenever it's useful.
+All the best with the agency's work either way.
+[Your name]</t>
+  </si>
+  <si>
+    <t>EMAIL 4 — TRIAL / WARM LEAD NUDGE (send once someone has started a free trial but hasn't sent a campaign)</t>
+  </si>
+  <si>
+    <t>Anything I can help set up?</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Saw you signed up for SendCleared — happy to help get your first client's inbox address connected if that'd save you time, or answer any questions about how the QA report works.
+Just reply here and I'll sort it.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Saw your team signed up for SendCleared — happy to help onboard your first couple of clients, or walk through the QA report and approval flow with your account managers if useful.
+Just reply here and I'll get it set up.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>EMAIL 5 — REFERRAL ASK (send to active/paying users)</t>
+  </si>
+  <si>
+    <t>Quick favour, if you don't mind</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Glad SendCleared's been useful. Quick ask — know any other freelancers who deal with the same client-approval headache? For every referral who signs up, I'll extend your plan free for a month.
+No worries at all if not — just thought I'd ask.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Glad SendCleared's been working well for your team. Quick ask — know any other agencies dealing with the same client sign-off chaos? For every referral who signs up, I'll extend your plan free for a month.
+No worries if not — just thought I'd ask.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>LinkedIn Content Plan — 10 articles</t>
+  </si>
+  <si>
+    <t>Scheduled into the Daily Plan tab (Monday content slots) across weeks 1-8</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Pillar</t>
+  </si>
+  <si>
+    <t>Angle / hook</t>
+  </si>
+  <si>
+    <t>Scheduled week</t>
+  </si>
+  <si>
+    <t>The £47 email mistake no one talks about</t>
+  </si>
+  <si>
+    <t>QA / mistakes</t>
+  </si>
+  <si>
+    <t>A single unresolved merge tag or broken link, multiplied across a whole list — the real cost of skipping QA.</t>
+  </si>
+  <si>
+    <t>Not started</t>
+  </si>
+  <si>
+    <t>Why 'looks approved' isn't the same as 'is approved'</t>
+  </si>
+  <si>
+    <t>Approval / accountability</t>
+  </si>
+  <si>
+    <t>The gap between a client skimming a Slack message and a client actually reviewing the send.</t>
+  </si>
+  <si>
+    <t>The 3 questions every client should ask before hitting send</t>
+  </si>
+  <si>
+    <t>A short, shareable checklist clients can use — positions the agency as the one who already asks these.</t>
+  </si>
+  <si>
+    <t>What I learned reviewing 500 client emails before they went out</t>
+  </si>
+  <si>
+    <t>Pattern-based lessons from common QA failures — broken personalization, missing alt text, bad preview text.</t>
+  </si>
+  <si>
+    <t>The hidden cost of 'just reply-all to approve'</t>
+  </si>
+  <si>
+    <t>Why informal approval chains create disputes later, and what a real audit trail looks like.</t>
+  </si>
+  <si>
+    <t>How agencies lose client trust in one broken subject line</t>
+  </si>
+  <si>
+    <t>Agency operations / trust</t>
+  </si>
+  <si>
+    <t>A single visible mistake and its outsized effect on a client relationship.</t>
+  </si>
+  <si>
+    <t>The pre-send checklist top email agencies actually use</t>
+  </si>
+  <si>
+    <t>A practical, tactical checklist post — highly shareable, doubles as a lead magnet.</t>
+  </si>
+  <si>
+    <t>Why your ESP can't catch these 5 mistakes (but your process should)</t>
+  </si>
+  <si>
+    <t>ESPs check deliverability, not content accuracy — the gap that pre-send QA fills.</t>
+  </si>
+  <si>
+    <t>The audit trail your client is quietly expecting</t>
+  </si>
+  <si>
+    <t>Clients increasingly expect proof of sign-off, especially after a mistake elsewhere burns them.</t>
+  </si>
+  <si>
+    <t>Week 7</t>
+  </si>
+  <si>
+    <t>From draft to approved: what a modern email workflow actually looks like</t>
+  </si>
+  <si>
+    <t>End-to-end narrative post — draft, QA, client approval link, send. Good for late-plan, when case studies exist.</t>
+  </si>
+  <si>
+    <t>Week 8</t>
+  </si>
+  <si>
+    <t>Profile</t>
+  </si>
+  <si>
+    <t>Tehseen Arbab</t>
+  </si>
+  <si>
+    <t>Chirag Kotadiya</t>
+  </si>
+  <si>
+    <t>Peter Kim</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Freelancer</t>
+  </si>
+  <si>
+    <t>Towfiqul Alam</t>
+  </si>
+  <si>
+    <t>Olivia Tildesley</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t>Narmin Fraint</t>
+  </si>
+  <si>
+    <t>Wassif A</t>
+  </si>
+  <si>
+    <t>Rachel Johnson</t>
+  </si>
+  <si>
+    <t>Ovi Akpojotor</t>
+  </si>
+  <si>
+    <t>William Ma</t>
+  </si>
+  <si>
+    <t>Judith Jornet Gomez</t>
+  </si>
+  <si>
+    <t>Arancha Gómez</t>
+  </si>
+  <si>
+    <t>Nils Goldingers</t>
+  </si>
+  <si>
+    <t>Ali Hassan</t>
+  </si>
+  <si>
+    <t>Wiktoria Wilczyńska</t>
+  </si>
+  <si>
+    <t>Aaron Magalong</t>
+  </si>
+  <si>
+    <t>Hannah Spicer</t>
+  </si>
+  <si>
+    <t>Holiness Godfrey</t>
+  </si>
+  <si>
+    <t>Luc de Bruin</t>
+  </si>
+  <si>
+    <t>Hamza Bukhari</t>
+  </si>
+  <si>
+    <t>Yurii Zuban</t>
+  </si>
+  <si>
+    <t>Lana Williams</t>
+  </si>
+  <si>
+    <t>Shaun Reynolds</t>
+  </si>
+  <si>
+    <t>Kate Reeves</t>
+  </si>
+  <si>
+    <t>Sylvester Swea</t>
+  </si>
+  <si>
+    <t>Louise Rebecca Thomas</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/victoriaapg1/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/queenofcrm/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/carmenemailmarketing/</t>
+  </si>
+  <si>
+    <t>Carmen Lee</t>
+  </si>
+  <si>
+    <t>Margaret Ward</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/margaret-ward-/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kehammond1/</t>
+  </si>
+  <si>
+    <t>Kate Hammond</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/chloe-mcleod-16841968/</t>
+  </si>
+  <si>
+    <t>Chloe McLeod</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/astra-tsangaris/</t>
+  </si>
+  <si>
+    <t>Astra Tsangaris</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/zoelacey/</t>
+  </si>
+  <si>
+    <t>Zoe Lacey</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/naomimdavies/</t>
+  </si>
+  <si>
+    <t>Naomi Davies</t>
+  </si>
+  <si>
+    <t>Phil Ireland</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sarah-brereton-b0199935/</t>
+  </si>
+  <si>
+    <t>Sarah Brereton</t>
+  </si>
+  <si>
+    <t>Victoria ap Gwynedd</t>
+  </si>
+  <si>
+    <t>Beth O'Malley</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/allanheo/</t>
+  </si>
+  <si>
+    <t>Allan Heo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/vernesacutuk/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/hsrivastava0205/</t>
+  </si>
+  <si>
+    <t>Harshita Srivastava</t>
+  </si>
+  <si>
+    <t>Vernesa Ćutuk</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/karantibdewal/</t>
+  </si>
+  <si>
+    <t>Karan Tibdewal</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sean-duffy-crm-email-marketing/</t>
+  </si>
+  <si>
+    <t>Sean Duffy</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jeannejennings/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeanne Jennings </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kathpay/</t>
+  </si>
+  <si>
+    <t>Kath Pay</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Israa A.</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/israaa/</t>
+  </si>
+  <si>
+    <t>ABDUL MOMEN</t>
+  </si>
+  <si>
+    <t>Andrew King</t>
+  </si>
+  <si>
+    <t>Anthony Hilary</t>
+  </si>
+  <si>
+    <t>Antony Newbold</t>
+  </si>
+  <si>
+    <t>Dan Tabaran</t>
+  </si>
+  <si>
+    <t>Dhikrullah Abimbola</t>
+  </si>
+  <si>
+    <t>Diego De Sevilla Acosta</t>
+  </si>
+  <si>
+    <t>Dikshika Routray</t>
+  </si>
+  <si>
+    <t>Elrize Erasmus</t>
+  </si>
+  <si>
+    <t>Emma Thao Nguyen</t>
+  </si>
+  <si>
+    <t>Haseeb Ahmed</t>
+  </si>
+  <si>
+    <t>Muhammad Muneeb</t>
+  </si>
+  <si>
+    <t>Jack Squire</t>
+  </si>
+  <si>
+    <t>Michelle Young</t>
+  </si>
+  <si>
+    <t>Milica Botha</t>
+  </si>
+  <si>
+    <t>Mohit Kumar</t>
+  </si>
+  <si>
+    <t>Natasha Weiss</t>
+  </si>
+  <si>
+    <t>Neha Gupta</t>
+  </si>
+  <si>
+    <t>Olimpia Valentina Chiriacescu</t>
+  </si>
+  <si>
+    <t>Pablo Martínez</t>
+  </si>
+  <si>
+    <t>Peter Nwede</t>
+  </si>
+  <si>
+    <t>Rhys Harris</t>
+  </si>
+  <si>
+    <t>Sonaton Mondol</t>
+  </si>
+  <si>
+    <t>Tais Tomazoni</t>
+  </si>
+  <si>
+    <t>Tom Nguyen</t>
+  </si>
+  <si>
+    <t>Tom Seebold</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+I noticed you do email marketing for clients — quick question: when a client signs off on a campaign, is that a proper approval, or more of a "looks good" reply over email or Slack?
+We built  SendCleared (sendcleared.com) to give freelancers a clean, timestamped approval link instead — it also runs a quick 14 point QA check before the client even sees it (broken links, missing alt text, personalization errors).
+a free trial is available to try on your next campaign — no card, no commitment. Would that be useful?
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+Just floating this back up in case it got buried. Free access to SendCleared.com is still open if useful — takes about 2 minutes to set up your first client, and works with whatever ESP you're using.
+I attached a quick one pager for you. No pressure either way — let me know if it's not a fit right now.
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lauren-barrett-708166163/</t>
+  </si>
+  <si>
+    <t>Lauren Barrett</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/danielwilcox32/</t>
+  </si>
+  <si>
+    <t>Daniel Wilcox</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jayde-laws-929311128/</t>
+  </si>
+  <si>
+    <t>Jayde Laws</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/george-lindh/</t>
+  </si>
+  <si>
+    <t>George Lindh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloudie Preuss </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/claudia-preuss-a4b310151/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/janagardiner/</t>
+  </si>
+  <si>
+    <t>Jana Gardiner</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/annettforcier/</t>
+  </si>
+  <si>
+    <t>Annett Forcier</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/harringtonben/</t>
+  </si>
+  <si>
+    <t>Ben Harrington</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jaspervanlaethem/</t>
+  </si>
+  <si>
+    <t>Jasper Van Laethem</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/email-love/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/badmarketing-digital/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/digitalmarketingcompanyagency/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/repuvue/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/aspen-marketing-services/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/alpha-co-marketing-media/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/less-is-moore-studios-email-marketing/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/progressive-marketing2020/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/marlomarketing/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/hiredigitalco/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/mavlers/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/vml/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/digitalzoneb2b/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/npdigital/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/elliot-digital/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/flowium/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/optimailonline/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/email-agency/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/chronosagency/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/email-data-group/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/b2i-digital/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/outcomes-rocket/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/retention-dot-com/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/brickmarketing/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/hawkemedia/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/risequadagency/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/valasys-media/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/apprise-marketing-services-ams/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/lilosocial/</t>
+  </si>
+  <si>
+    <t>Emailed (Linkedin)</t>
+  </si>
+  <si>
+    <t>Hi [Name], I built SendCleared — a tool that runs a pre-send QA check and gets client sign-off on every email campaign, whatever ESP you use. Would love to connect with other email freelancers.</t>
+  </si>
+  <si>
+    <t>Connect Request</t>
+  </si>
+  <si>
+    <t>05.09.26</t>
+  </si>
+  <si>
+    <t>07.09.26</t>
+  </si>
+  <si>
+    <t>Hi [Name],
+I'm the founder of SendCleared (sendcleared.com) — it runs a QA check on every email campaign and gets client sign-off through a single branded link, regardless of which ESP you use.
+I thought this might save your account managers the back-and-forth of chasing approval over Slack or email threads.
+There's a 14 day free trial available — no credit card, no commitment.
+Would that be useful?
+Best,
+[Your name]</t>
+  </si>
+  <si>
+    <t>Perfit Email Marketing</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/abril-herrera-dorna/</t>
+  </si>
+  <si>
+    <t>Abril Herrera Dorna</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mayra-altamirano-perfit/</t>
+  </si>
+  <si>
+    <t>Mayra Altamirano</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/fernandezwalter/?locale=en</t>
+  </si>
+  <si>
+    <t>Walter Fernández</t>
+  </si>
+  <si>
+    <t>Selzy | Email Marketing</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nataliia-hushkovska/</t>
+  </si>
+  <si>
+    <t>Nataliia Hushkovska</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/alexkachalov/</t>
+  </si>
+  <si>
+    <t>Alexey Kachalov</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/christine-hombrink/</t>
+  </si>
+  <si>
+    <t>Robly Email Marketing</t>
+  </si>
+  <si>
+    <t>Christine (Allen) Hombrink</t>
+  </si>
+  <si>
+    <t>Email Marketing Solutions</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/betty-p-carpenter-503806154/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/souhail-hadouch-226a22161/</t>
+  </si>
+  <si>
+    <t>Rotney Jacob</t>
+  </si>
+  <si>
+    <t>Betty P. Carpenter</t>
+  </si>
+  <si>
+    <t>Souhail Hadouch</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rotney-jacob-743744108/</t>
+  </si>
+  <si>
+    <t>Insendra</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jeremy-fleming-311b81198/</t>
+  </si>
+  <si>
+    <t>Jeremy Fleming</t>
+  </si>
+  <si>
+    <t>Essence of Email</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/xiaohuiw/</t>
+  </si>
+  <si>
+    <t>Xiaohui "X" Wang</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/philip-mbwaya-ab593758/</t>
+  </si>
+  <si>
+    <t>Philip Mbwaya</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dabhi-bhumil-6427a01b7/</t>
+  </si>
+  <si>
+    <t>Dabhi Bhumil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firedrum </t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/daniel-anzalone/</t>
+  </si>
+  <si>
+    <t>Daniel Anzalone</t>
+  </si>
+  <si>
+    <t>Kevin Troendle</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kevin-troendle-b3782a2b/</t>
+  </si>
+  <si>
+    <t>The Email Marketers</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/adel-gouida-1aa4a61b8/</t>
+  </si>
+  <si>
+    <t>Adel Gouida</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/aneela-rana-22120a31b/</t>
+  </si>
+  <si>
+    <t>Aneela Rana</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/stevanovic-nenad/</t>
+  </si>
+  <si>
+    <t>Nenad Stevanović</t>
+  </si>
+  <si>
+    <t>Email Allstars</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/patricia-cabrera-768202179/</t>
+  </si>
+  <si>
+    <t>Patricia Cabrera</t>
+  </si>
+  <si>
+    <t>Email Industries</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sriramgangs/</t>
+  </si>
+  <si>
+    <t>Sriram G</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rafsan-jamil-625842379/</t>
+  </si>
+  <si>
+    <t>Rafsan Jamil</t>
+  </si>
+  <si>
+    <t>Mavlers</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rushabh-shah-8a8537143/</t>
+  </si>
+  <si>
+    <t>Rushabh Shah</t>
+  </si>
+  <si>
+    <t>Social Scout Email Marketing</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tiernan-corcoran-6a65b4373/</t>
+  </si>
+  <si>
+    <t>Tiernan Corcoran</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/monicanaidoo/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mónica Naidoo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/feryhdz/</t>
+  </si>
+  <si>
+    <t>Maria Fernanda (Fery) Hernandez Diaz</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mariamarafante/</t>
+  </si>
+  <si>
+    <t>Maria M</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mayur-prajapati-4a7b86256/</t>
+  </si>
+  <si>
+    <t>Mayur Prajapati</t>
+  </si>
+  <si>
+    <t>RankFast | Search Marketing Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CANZ Marketing</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/christina-dali-7a5539210/</t>
+  </si>
+  <si>
+    <t>Christina Dali</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/abby-bruke-95a273210/</t>
+  </si>
+  <si>
+    <t>Abby Bruke</t>
+  </si>
+  <si>
+    <t>No Limit Email</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ecom-michael-galvin/</t>
+  </si>
+  <si>
+    <t>Michael Galvin</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tatiana-garcia-posada/</t>
+  </si>
+  <si>
+    <t>Tatiana García Posada</t>
+  </si>
+  <si>
+    <t>Benchmark Email</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/raquelherrerahdez/?locale=en</t>
+  </si>
+  <si>
+    <t>Raquel Herrera Hernández</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jessica-lunk-39391017/</t>
+  </si>
+  <si>
+    <t>Jessica Lunk</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/daniela-canob/</t>
+  </si>
+  <si>
+    <t>Daniela Cano</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/surender-kumar8/</t>
+  </si>
+  <si>
+    <t>Surender Kumar</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/anna-rose-elkins-93baa011b/</t>
+  </si>
+  <si>
+    <t>BAD Marketing</t>
+  </si>
+  <si>
+    <t>Anna Rose Elkins</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kelsey-carstens/</t>
+  </si>
+  <si>
+    <t>Kelsey Carstens</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/peter-gonglach/</t>
+  </si>
+  <si>
+    <t>Peter Gonglach</t>
+  </si>
+  <si>
+    <t>RepuVue Marketing Agency</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/emily-godwin-84a57b74/</t>
+  </si>
+  <si>
+    <t>Emily Godwin</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/angelaspeziale/</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Angela Speziale</t>
+  </si>
+  <si>
+    <t>Alpha Co. Marketing &amp; Media</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ghulam-akbar-6273b3341/</t>
+  </si>
+  <si>
+    <t>Ghulam Akbar</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mat%C3%ADas-nahuel-rizzi-del-r%C3%ADo-b749aa18b/?locale=en</t>
+  </si>
+  <si>
+    <t>Matías Nahuel Rizzi del Río</t>
+  </si>
+  <si>
+    <t>Less Is Moore Email Marketing</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ekeh-paul-2288a3215/</t>
+  </si>
+  <si>
+    <t>Ekeh Paul</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/chloejpg/</t>
+  </si>
+  <si>
+    <t>Chloe L</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/spencer-moore-37a993245/</t>
+  </si>
+  <si>
+    <t>Spencer Moore</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +2124,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\ mmm\ yy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1209,8 +2191,56 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF134E8E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF5A5A56"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF134E8E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF5A5A56"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1241,6 +2271,18 @@
         <bgColor rgb="FFFFF6E5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF134E8E"/>
+        <bgColor rgb="FF333399"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F7F5"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1269,7 +2311,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1298,19 +2340,39 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1589,30 +2651,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1644,24 +2706,24 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
     </row>
     <row r="6" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>1</v>
       </c>
       <c r="B6" s="3">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>12</v>
@@ -1688,7 +2750,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="3">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>18</v>
@@ -1715,7 +2777,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="3">
-        <v>46232</v>
+        <v>46263</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>21</v>
@@ -1742,7 +2804,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="3">
-        <v>46233</v>
+        <v>46264</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>25</v>
@@ -1769,7 +2831,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="3">
-        <v>46234</v>
+        <v>46265</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>28</v>
@@ -1792,24 +2854,24 @@
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>6</v>
       </c>
       <c r="B12" s="3">
-        <v>46237</v>
+        <v>46266</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>32</v>
@@ -1836,7 +2898,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="3">
-        <v>46238</v>
+        <v>46267</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>37</v>
@@ -1863,7 +2925,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="3">
-        <v>46239</v>
+        <v>46268</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>41</v>
@@ -1890,7 +2952,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="3">
-        <v>46240</v>
+        <v>46269</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -1917,7 +2979,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="3">
-        <v>46241</v>
+        <v>46270</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>49</v>
@@ -1940,24 +3002,24 @@
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
+      <c r="A17" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>11</v>
       </c>
       <c r="B18" s="3">
-        <v>46244</v>
+        <v>46271</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>55</v>
@@ -1984,7 +3046,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="3">
-        <v>46245</v>
+        <v>46272</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>60</v>
@@ -2011,7 +3073,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="3">
-        <v>46246</v>
+        <v>46273</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>64</v>
@@ -2038,7 +3100,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="3">
-        <v>46247</v>
+        <v>46274</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>69</v>
@@ -2065,7 +3127,7 @@
         <v>15</v>
       </c>
       <c r="B22" s="3">
-        <v>46248</v>
+        <v>46275</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>73</v>
@@ -2088,24 +3150,24 @@
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
+      <c r="A23" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
     </row>
     <row r="24" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>16</v>
       </c>
       <c r="B24" s="3">
-        <v>46251</v>
+        <v>46276</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>78</v>
@@ -2132,7 +3194,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="3">
-        <v>46252</v>
+        <v>46277</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>83</v>
@@ -2159,7 +3221,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="3">
-        <v>46253</v>
+        <v>46278</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>87</v>
@@ -2186,7 +3248,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="3">
-        <v>46254</v>
+        <v>46279</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>91</v>
@@ -2213,7 +3275,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="3">
-        <v>46255</v>
+        <v>46280</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>95</v>
@@ -2236,24 +3298,24 @@
       <c r="I28" s="4"/>
     </row>
     <row r="29" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="30" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>21</v>
       </c>
       <c r="B30" s="3">
-        <v>46258</v>
+        <v>46281</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>101</v>
@@ -2280,7 +3342,7 @@
         <v>22</v>
       </c>
       <c r="B31" s="3">
-        <v>46259</v>
+        <v>46282</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>106</v>
@@ -2307,7 +3369,7 @@
         <v>23</v>
       </c>
       <c r="B32" s="3">
-        <v>46260</v>
+        <v>46283</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>110</v>
@@ -2334,7 +3396,7 @@
         <v>24</v>
       </c>
       <c r="B33" s="3">
-        <v>46261</v>
+        <v>46284</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>114</v>
@@ -2361,7 +3423,7 @@
         <v>25</v>
       </c>
       <c r="B34" s="3">
-        <v>46262</v>
+        <v>46285</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>119</v>
@@ -2384,24 +3446,24 @@
       <c r="I34" s="4"/>
     </row>
     <row r="35" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21"/>
+      <c r="D35" s="21"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21"/>
+      <c r="G35" s="21"/>
+      <c r="H35" s="21"/>
+      <c r="I35" s="21"/>
     </row>
     <row r="36" spans="1:9" ht="45.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>26</v>
       </c>
       <c r="B36" s="3">
-        <v>46265</v>
+        <v>46286</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>124</v>
@@ -2428,7 +3490,7 @@
         <v>27</v>
       </c>
       <c r="B37" s="3">
-        <v>46266</v>
+        <v>46287</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>129</v>
@@ -2455,7 +3517,7 @@
         <v>28</v>
       </c>
       <c r="B38" s="3">
-        <v>46267</v>
+        <v>46288</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>133</v>
@@ -2482,7 +3544,7 @@
         <v>29</v>
       </c>
       <c r="B39" s="3">
-        <v>46268</v>
+        <v>46289</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>137</v>
@@ -2509,7 +3571,7 @@
         <v>30</v>
       </c>
       <c r="B40" s="3">
-        <v>46269</v>
+        <v>46290</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>141</v>
@@ -2544,6 +3606,2029 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
+  <dimension ref="A1:I163"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="58" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.5" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>149</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>554</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2" s="19"/>
+      <c r="D2" t="s">
+        <v>454</v>
+      </c>
+      <c r="F2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" t="s">
+        <v>429</v>
+      </c>
+      <c r="E3" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" t="s">
+        <v>416</v>
+      </c>
+      <c r="D4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>441</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C6" s="19"/>
+      <c r="D6" t="s">
+        <v>467</v>
+      </c>
+      <c r="E6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" t="s">
+        <v>416</v>
+      </c>
+      <c r="D7" t="s">
+        <v>417</v>
+      </c>
+      <c r="E7" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>333</v>
+      </c>
+      <c r="B8" t="s">
+        <v>416</v>
+      </c>
+      <c r="D8" t="s">
+        <v>412</v>
+      </c>
+      <c r="E8" t="s">
+        <v>557</v>
+      </c>
+      <c r="H8" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>349</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C9" s="19"/>
+      <c r="D9" t="s">
+        <v>439</v>
+      </c>
+      <c r="E9" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>470</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" t="s">
+        <v>471</v>
+      </c>
+      <c r="F11" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C12" s="19"/>
+      <c r="D12" t="s">
+        <v>459</v>
+      </c>
+      <c r="F12" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>320</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C13" s="19"/>
+      <c r="D13" t="s">
+        <v>457</v>
+      </c>
+      <c r="E13" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>341</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" t="s">
+        <v>423</v>
+      </c>
+      <c r="E14" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C15" s="19"/>
+      <c r="D15" t="s">
+        <v>427</v>
+      </c>
+      <c r="H15" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>330</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" t="s">
+        <v>496</v>
+      </c>
+      <c r="E16" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>324</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" t="s">
+        <v>495</v>
+      </c>
+      <c r="E17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>455</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C18" s="19"/>
+      <c r="D18" t="s">
+        <v>456</v>
+      </c>
+      <c r="F18" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>300</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" t="s">
+        <v>490</v>
+      </c>
+      <c r="E19" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C20" s="19"/>
+      <c r="D20" t="s">
+        <v>494</v>
+      </c>
+      <c r="E20" t="s">
+        <v>557</v>
+      </c>
+      <c r="I20" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="19"/>
+      <c r="D21" t="s">
+        <v>493</v>
+      </c>
+      <c r="E21" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>446</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" t="s">
+        <v>445</v>
+      </c>
+      <c r="E22" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>328</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C23" s="19"/>
+      <c r="D23" t="s">
+        <v>433</v>
+      </c>
+      <c r="E23" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>350</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" t="s">
+        <v>440</v>
+      </c>
+      <c r="E24" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>474</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" t="s">
+        <v>475</v>
+      </c>
+      <c r="E25" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>348</v>
+      </c>
+      <c r="B26" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C26" s="19"/>
+      <c r="D26" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>447</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" t="s">
+        <v>448</v>
+      </c>
+      <c r="E27" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>468</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C28" s="19"/>
+      <c r="D28" t="s">
+        <v>469</v>
+      </c>
+      <c r="E28" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>343</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" s="19"/>
+      <c r="D29" t="s">
+        <v>425</v>
+      </c>
+      <c r="E29" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>472</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C30" s="19"/>
+      <c r="D30" t="s">
+        <v>473</v>
+      </c>
+      <c r="E30" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>323</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" t="s">
+        <v>432</v>
+      </c>
+      <c r="E32" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>317</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" t="s">
+        <v>489</v>
+      </c>
+      <c r="E33" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>465</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" t="s">
+        <v>466</v>
+      </c>
+      <c r="E34" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>308</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C35" s="19"/>
+      <c r="D35" t="s">
+        <v>431</v>
+      </c>
+      <c r="G35" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C36" s="19"/>
+      <c r="D36" t="s">
+        <v>434</v>
+      </c>
+      <c r="E36" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>298</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C37" s="19"/>
+      <c r="D37" t="s">
+        <v>486</v>
+      </c>
+      <c r="E37" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>312</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C38" s="19"/>
+      <c r="D38" t="s">
+        <v>485</v>
+      </c>
+      <c r="E38" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>299</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C39" s="19"/>
+      <c r="D39" t="s">
+        <v>484</v>
+      </c>
+      <c r="E39" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>314</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" t="s">
+        <v>483</v>
+      </c>
+      <c r="E40" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>449</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C41" s="19"/>
+      <c r="D41" t="s">
+        <v>450</v>
+      </c>
+      <c r="E41" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>334</v>
+      </c>
+      <c r="B42" t="s">
+        <v>416</v>
+      </c>
+      <c r="D42" t="s">
+        <v>413</v>
+      </c>
+      <c r="E42" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>443</v>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C43" s="19"/>
+      <c r="D43" t="s">
+        <v>444</v>
+      </c>
+      <c r="E43" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>442</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C44" s="19"/>
+      <c r="D44" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>451</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C45" s="19"/>
+      <c r="D45" t="s">
+        <v>452</v>
+      </c>
+      <c r="E45" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>318</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C46" s="19"/>
+      <c r="D46" t="s">
+        <v>482</v>
+      </c>
+      <c r="E46" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C47" s="19"/>
+      <c r="D47" t="s">
+        <v>481</v>
+      </c>
+      <c r="E47" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>329</v>
+      </c>
+      <c r="B48" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C48" s="19"/>
+      <c r="D48" t="s">
+        <v>480</v>
+      </c>
+      <c r="E48" t="s">
+        <v>558</v>
+      </c>
+      <c r="F48" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>462</v>
+      </c>
+      <c r="B49" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C49" s="19"/>
+      <c r="D49" t="s">
+        <v>463</v>
+      </c>
+      <c r="E49" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C50" s="19"/>
+      <c r="D50" t="s">
+        <v>428</v>
+      </c>
+      <c r="E50" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>325</v>
+      </c>
+      <c r="B51" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C51" s="19"/>
+      <c r="D51" t="s">
+        <v>479</v>
+      </c>
+      <c r="E51" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" t="s">
+        <v>430</v>
+      </c>
+      <c r="E52" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>316</v>
+      </c>
+      <c r="B53" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" t="s">
+        <v>499</v>
+      </c>
+      <c r="E53" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>319</v>
+      </c>
+      <c r="B54" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" t="s">
+        <v>501</v>
+      </c>
+      <c r="E54" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>321</v>
+      </c>
+      <c r="B55" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" t="s">
+        <v>502</v>
+      </c>
+      <c r="E55" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>305</v>
+      </c>
+      <c r="B56" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" t="s">
+        <v>503</v>
+      </c>
+      <c r="E56" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>304</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" t="s">
+        <v>504</v>
+      </c>
+      <c r="E57" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>517</v>
+      </c>
+      <c r="B58" t="s">
+        <v>416</v>
+      </c>
+      <c r="D58" t="s">
+        <v>518</v>
+      </c>
+      <c r="E58" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>519</v>
+      </c>
+      <c r="B59" t="s">
+        <v>416</v>
+      </c>
+      <c r="D59" t="s">
+        <v>520</v>
+      </c>
+      <c r="E59" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>521</v>
+      </c>
+      <c r="B60" t="s">
+        <v>416</v>
+      </c>
+      <c r="D60" t="s">
+        <v>522</v>
+      </c>
+      <c r="E60" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>523</v>
+      </c>
+      <c r="B61" t="s">
+        <v>416</v>
+      </c>
+      <c r="D61" t="s">
+        <v>524</v>
+      </c>
+      <c r="E61" t="s">
+        <v>558</v>
+      </c>
+      <c r="H61" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>507</v>
+      </c>
+      <c r="B62" t="s">
+        <v>416</v>
+      </c>
+      <c r="D62" t="s">
+        <v>508</v>
+      </c>
+      <c r="E62" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>511</v>
+      </c>
+      <c r="B63" t="s">
+        <v>416</v>
+      </c>
+      <c r="D63" t="s">
+        <v>512</v>
+      </c>
+      <c r="E63" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>513</v>
+      </c>
+      <c r="B64" t="s">
+        <v>416</v>
+      </c>
+      <c r="D64" t="s">
+        <v>514</v>
+      </c>
+      <c r="E64" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>516</v>
+      </c>
+      <c r="B65" t="s">
+        <v>416</v>
+      </c>
+      <c r="D65" t="s">
+        <v>515</v>
+      </c>
+      <c r="E65" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>342</v>
+      </c>
+      <c r="B67" t="s">
+        <v>419</v>
+      </c>
+      <c r="D67" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" t="s">
+        <v>419</v>
+      </c>
+      <c r="D68" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>337</v>
+      </c>
+      <c r="B69" t="s">
+        <v>419</v>
+      </c>
+      <c r="D69" s="18" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>344</v>
+      </c>
+      <c r="B70" t="s">
+        <v>419</v>
+      </c>
+      <c r="D70" t="s">
+        <v>426</v>
+      </c>
+      <c r="H70" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>345</v>
+      </c>
+      <c r="B72" t="s">
+        <v>166</v>
+      </c>
+      <c r="D72" t="s">
+        <v>435</v>
+      </c>
+      <c r="E72" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>335</v>
+      </c>
+      <c r="B73" t="s">
+        <v>166</v>
+      </c>
+      <c r="D73" t="s">
+        <v>414</v>
+      </c>
+      <c r="E73" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>338</v>
+      </c>
+      <c r="B74" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74" t="s">
+        <v>420</v>
+      </c>
+      <c r="E74" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>313</v>
+      </c>
+      <c r="B75" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" s="19"/>
+      <c r="D75" t="s">
+        <v>492</v>
+      </c>
+      <c r="E75" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>446</v>
+      </c>
+      <c r="B76" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="19"/>
+      <c r="D76" t="s">
+        <v>445</v>
+      </c>
+      <c r="E76" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>346</v>
+      </c>
+      <c r="B77" t="s">
+        <v>166</v>
+      </c>
+      <c r="D77" t="s">
+        <v>436</v>
+      </c>
+      <c r="E77" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>311</v>
+      </c>
+      <c r="B78" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C78" s="19"/>
+      <c r="D78" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>322</v>
+      </c>
+      <c r="B79" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C79" s="19"/>
+      <c r="D79" t="s">
+        <v>488</v>
+      </c>
+      <c r="E79" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>327</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C80" s="19"/>
+      <c r="D80" t="s">
+        <v>487</v>
+      </c>
+      <c r="E80" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>309</v>
+      </c>
+      <c r="B81" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C81" s="19"/>
+      <c r="D81" t="s">
+        <v>498</v>
+      </c>
+      <c r="E81" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>310</v>
+      </c>
+      <c r="B82" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="19"/>
+      <c r="D82" t="s">
+        <v>500</v>
+      </c>
+      <c r="E82" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>509</v>
+      </c>
+      <c r="B83" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" t="s">
+        <v>510</v>
+      </c>
+      <c r="E83" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>315</v>
+      </c>
+      <c r="B84" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C84" s="19"/>
+      <c r="D84" t="s">
+        <v>497</v>
+      </c>
+      <c r="E84" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>561</v>
+      </c>
+      <c r="B85" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" t="s">
+        <v>560</v>
+      </c>
+      <c r="D85" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>563</v>
+      </c>
+      <c r="B86" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C86" t="s">
+        <v>560</v>
+      </c>
+      <c r="D86" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>565</v>
+      </c>
+      <c r="B87" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C87" t="s">
+        <v>560</v>
+      </c>
+      <c r="D87" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>568</v>
+      </c>
+      <c r="B88" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C88" t="s">
+        <v>567</v>
+      </c>
+      <c r="D88" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>570</v>
+      </c>
+      <c r="B89" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C89" t="s">
+        <v>567</v>
+      </c>
+      <c r="D89" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>572</v>
+      </c>
+      <c r="B90" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C90" t="s">
+        <v>573</v>
+      </c>
+      <c r="D90" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>576</v>
+      </c>
+      <c r="B91" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" t="s">
+        <v>575</v>
+      </c>
+      <c r="D91" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>577</v>
+      </c>
+      <c r="B92" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" t="s">
+        <v>575</v>
+      </c>
+      <c r="D92" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>581</v>
+      </c>
+      <c r="B93" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C93" t="s">
+        <v>575</v>
+      </c>
+      <c r="D93" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>583</v>
+      </c>
+      <c r="B94" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C94" t="s">
+        <v>582</v>
+      </c>
+      <c r="D94" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>586</v>
+      </c>
+      <c r="B95" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C95" t="s">
+        <v>585</v>
+      </c>
+      <c r="D95" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>588</v>
+      </c>
+      <c r="B96" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C96" t="s">
+        <v>585</v>
+      </c>
+      <c r="D96" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>590</v>
+      </c>
+      <c r="B97" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C97" t="s">
+        <v>585</v>
+      </c>
+      <c r="D97" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>593</v>
+      </c>
+      <c r="B98" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C98" t="s">
+        <v>592</v>
+      </c>
+      <c r="D98" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>596</v>
+      </c>
+      <c r="B99" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C99" t="s">
+        <v>592</v>
+      </c>
+      <c r="D99" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="32" t="s">
+        <v>598</v>
+      </c>
+      <c r="B100" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C100" t="s">
+        <v>597</v>
+      </c>
+      <c r="D100" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="32" t="s">
+        <v>600</v>
+      </c>
+      <c r="B101" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C101" t="s">
+        <v>597</v>
+      </c>
+      <c r="D101" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="32" t="s">
+        <v>602</v>
+      </c>
+      <c r="B102" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" t="s">
+        <v>597</v>
+      </c>
+      <c r="D102" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>605</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C103" t="s">
+        <v>604</v>
+      </c>
+      <c r="D103" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>608</v>
+      </c>
+      <c r="B104" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C104" t="s">
+        <v>607</v>
+      </c>
+      <c r="D104" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>610</v>
+      </c>
+      <c r="B105" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C105" t="s">
+        <v>607</v>
+      </c>
+      <c r="D105" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>613</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C106" t="s">
+        <v>612</v>
+      </c>
+      <c r="D106" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>335</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C107" t="s">
+        <v>612</v>
+      </c>
+      <c r="D107" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>616</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C108" t="s">
+        <v>615</v>
+      </c>
+      <c r="D108" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>618</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C109" t="s">
+        <v>615</v>
+      </c>
+      <c r="D109" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>620</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C110" t="s">
+        <v>615</v>
+      </c>
+      <c r="D110" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>622</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C111" t="s">
+        <v>615</v>
+      </c>
+      <c r="D111" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>624</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C112" t="s">
+        <v>626</v>
+      </c>
+      <c r="D112" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>628</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C113" t="s">
+        <v>627</v>
+      </c>
+      <c r="D113" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>630</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C114" t="s">
+        <v>627</v>
+      </c>
+      <c r="D114" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>633</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C115" t="s">
+        <v>632</v>
+      </c>
+      <c r="D115" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>635</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C116" t="s">
+        <v>632</v>
+      </c>
+      <c r="D116" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>638</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C117" t="s">
+        <v>637</v>
+      </c>
+      <c r="D117" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>640</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C118" t="s">
+        <v>637</v>
+      </c>
+      <c r="D118" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>642</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C119" t="s">
+        <v>637</v>
+      </c>
+      <c r="D119" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>644</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C120" t="s">
+        <v>637</v>
+      </c>
+      <c r="D120" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>646</v>
+      </c>
+      <c r="B121" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C121" t="s">
+        <v>647</v>
+      </c>
+      <c r="D121" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>649</v>
+      </c>
+      <c r="B122" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C122" t="s">
+        <v>647</v>
+      </c>
+      <c r="D122" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>651</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C123" t="s">
+        <v>647</v>
+      </c>
+      <c r="D123" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>654</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C124" t="s">
+        <v>653</v>
+      </c>
+      <c r="D124" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>656</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C125" t="s">
+        <v>653</v>
+      </c>
+      <c r="D125" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>659</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C126" t="s">
+        <v>658</v>
+      </c>
+      <c r="D126" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>661</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C127" t="s">
+        <v>658</v>
+      </c>
+      <c r="D127" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="32" t="s">
+        <v>664</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C128" t="s">
+        <v>663</v>
+      </c>
+      <c r="D128" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>666</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C129" t="s">
+        <v>663</v>
+      </c>
+      <c r="D129" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="32" t="s">
+        <v>668</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C130" t="s">
+        <v>663</v>
+      </c>
+      <c r="D130" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B131" s="19"/>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>532</v>
+      </c>
+      <c r="D135" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A161" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A162" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A163" t="s">
+        <v>553</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D82">
+    <sortCondition descending="1" ref="B2:B82"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2565,40 +5650,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
-      <c r="N3" s="16"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
     </row>
     <row r="4" spans="1:15" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4618,129 +7703,304 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="100" customWidth="1"/>
+    <col min="2" max="2" width="76.6640625" customWidth="1"/>
+    <col min="3" max="3" width="67.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="15"/>
+      <c r="B1" s="22"/>
     </row>
     <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="14"/>
+      <c r="B4" s="21"/>
     </row>
     <row r="5" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>177</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>178</v>
+        <v>555</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="B6" s="4" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="21" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="14"/>
+      <c r="B8" s="21"/>
     </row>
     <row r="9" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B10" s="4" t="s">
+    </row>
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="21" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="B12" s="14"/>
+      <c r="B12" s="21"/>
     </row>
     <row r="13" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="B14" s="4" t="s">
+    </row>
+    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="21" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="B16" s="21"/>
+    </row>
+    <row r="17" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="14"/>
-    </row>
-    <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="7" t="s">
+      <c r="B17" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B17" s="4" t="s">
+    </row>
+    <row r="18" spans="1:3" ht="180" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="7" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="180" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="7" t="s">
+      <c r="B18" s="4" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B20" s="21"/>
+    </row>
+    <row r="21" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="7" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14" t="s">
+      <c r="B21" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B20" s="14"/>
-    </row>
-    <row r="21" spans="1:2" ht="135" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>198</v>
+    </row>
+    <row r="24" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="A24" s="24" t="s">
+        <v>351</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="25" t="s">
+        <v>352</v>
+      </c>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="B27" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+    </row>
+    <row r="29" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A29" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="240" x14ac:dyDescent="0.2">
+      <c r="A30" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+    </row>
+    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+      <c r="A34" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="B36" s="21"/>
+      <c r="C36" s="21"/>
+    </row>
+    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="144" x14ac:dyDescent="0.2">
+      <c r="A38" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+    </row>
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="B44" s="21"/>
+      <c r="C44" s="21"/>
+    </row>
+    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="160" x14ac:dyDescent="0.2">
+      <c r="A46" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>377</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="13">
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -4760,44 +8020,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
+      <c r="A1" s="22" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E4" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -5081,24 +8341,24 @@
       <c r="E45" s="6"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="17" t="s">
+      <c r="A47" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="B47" s="26"/>
+      <c r="D47" s="26" t="s">
+        <v>206</v>
+      </c>
+      <c r="E47" s="26"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="B47" s="17"/>
-      <c r="D47" s="17" t="s">
+      <c r="B48" s="27"/>
+      <c r="D48" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="E47" s="17"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="B48" s="18"/>
-      <c r="D48" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="E48" s="18"/>
+      <c r="E48" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5123,50 +8383,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
+      <c r="A1" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B4" s="10">
         <v>0</v>
@@ -5196,7 +8456,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B5" s="12">
         <v>0</v>
@@ -5226,7 +8486,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B6" s="10">
         <v>0</v>
@@ -5256,7 +8516,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="12">
         <v>0</v>
@@ -5286,7 +8546,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B8" s="10">
         <v>0</v>
@@ -5316,7 +8576,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B9" s="12">
         <v>0</v>
@@ -5346,7 +8606,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B10" s="10">
         <v>0</v>
@@ -5376,7 +8636,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B11" s="12">
         <v>0</v>
@@ -5406,7 +8666,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B12" s="10">
         <v>0</v>
@@ -5436,7 +8696,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B13" s="12">
         <v>0</v>
@@ -5465,17 +8725,17 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="26.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
+      <c r="A15" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5500,103 +8760,103 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>232</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
+      <c r="A1" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="D5" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="E5" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="G5" s="13" t="s">
         <v>250</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>16</v>
@@ -5604,45 +8864,45 @@
     </row>
     <row r="7" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>258</v>
+      </c>
+      <c r="D7" s="13" t="s">
         <v>259</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="C7" s="13" t="s">
+      <c r="E7" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>261</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>262</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>16</v>
@@ -5650,22 +8910,22 @@
     </row>
     <row r="9" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>270</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="D9" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="E9" s="13" t="s">
         <v>272</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="F9" s="13" t="s">
         <v>273</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>275</v>
       </c>
       <c r="G9" s="13" t="s">
         <v>16</v>
@@ -5673,22 +8933,22 @@
     </row>
     <row r="10" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="F10" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>281</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>16</v>
@@ -5704,6 +8964,273 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D9436A-E997-3C40-A694-C3E3FD008A15}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="6" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="29" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="29"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="30" t="s">
+        <v>379</v>
+      </c>
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>381</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>384</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A5" s="6">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>390</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="6">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A8" s="16">
+        <v>4</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>395</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A9" s="6">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>6</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A11" s="6">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A12" s="16">
+        <v>8</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A13" s="6">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A14" s="16">
+        <v>10</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>388</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="F5:F14" xr:uid="{6C3535FD-B498-D849-A861-F6515FFD4150}">
+      <formula1>"Not started,Drafted,Published,Skipped"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5714,63 +9241,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>282</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="A1" s="22" t="s">
+        <v>280</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="2" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="A2" s="31" t="s">
+        <v>281</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C5" s="6"/>
     </row>
     <row r="6" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C8" s="6"/>
     </row>
@@ -5784,7 +9311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -5795,32 +9322,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>295</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
+      <c r="A1" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>169</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -6030,369 +9557,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C59208D-E153-D94F-949B-1D2F26D7FF23}">
-  <dimension ref="A1:A71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>357</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>